--- a/hosting/scripts/hosting-jagt.xlsx
+++ b/hosting/scripts/hosting-jagt.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,9 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="0010B981"/>
+    </font>
+    <font>
       <color rgb="0010B981"/>
     </font>
   </fonts>
@@ -83,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -91,13 +94,8 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -467,7 +465,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -569,7 +567,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>hosting_jagt.db (SQLite3)</t>
+          <t>hosting_jagt.db</t>
         </is>
       </c>
     </row>
@@ -581,7 +579,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2026-03-21 16:28:27</t>
+          <t>2026-03-22 10:19:14</t>
         </is>
       </c>
     </row>
@@ -599,19 +597,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
     <col width="35" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -632,7 +631,7 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>Repo GitHub</t>
+          <t>Repo</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
@@ -652,465 +651,515 @@
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
-          <t>Frecuencia</t>
+          <t>Frec</t>
         </is>
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
+          <t>Sheet ID</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Creada</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>JAGT Landing Page</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>josegart.streamlit.app</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>jagt2024/Reservar/pagina_web/jagt_landing.py</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>streamlit</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>16F7ncXQJVmUJMMsl1So8FdfRZX9Vlo_nHkL9pWULjSE/edit?gid=855258571#gid=855258571</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>Página web personal JAGT</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Agenda Empresa serv.</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>josegart-agenda.streamlit.app</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>jagt2024/Reservar/Agenda/main_agenda.py</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>streamlit</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>13UqQN6VXO9vTDIhyAEON9Qf5SD-1tgGgDA-Zo38udso/edit?gid=163711379#gid=163711379</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>Empresas de Servicios temporales</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Admon Conjuntos</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>josegart-conjuntos.streamlit.app</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>jagt2024/Reservar/Admon-Conjuntos/main_conjunto_cb.py</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>streamlit</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>1UqCfVwwQfAkzRHG4_YCX8BD3Xl95KB7qvwjZNXWkzKw/edit?gid=210975473#gid=210975473</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>Sistema de administracion de conjuntos</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Panel Hosting</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>josegart-hosting.streamlit.app</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>jagt2024/Reservar/hosting/app.py</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>streamlit</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>1PXLNO-QL4bIqD_R4awEK71OunP7AUCysSZ5nWk4PqB0/edit?gid=1502391982#gid=1502391982</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>Panel de control del hosting</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Productos de Aseo</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>josegart-claridad.streamlit.app</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>jagt2024/Reservar/claridad/main_emp_cld.py</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>streamlit</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>1SKW_Tmk2H2V4OGKaELmVsvRmEe2x8UJJAKPdpTRimNg/edit?gid=1910642720#gid=1910642720</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>Venta de productos de aseo</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Clinica de Psicologia</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>josegart-clinica.streamlit.app</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>jagt2024/Reservar/Clinica-Amor/main_emp_amo.py</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>streamlit</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>19FjdgHOjwbrilbhBuNhn7cFwTzKqy7cabh1Nc6QQCv4/edit?gid=0#gid=0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>Gestion Clientes e Historias Clinicas</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Plataforma Autos Particulares</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>josegar-autos.streamlit.app</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>jagt2024/Reservar/DP-Andres/main_emp_dp.py</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>streamlit</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>18Xzq0almiDk740OyywLTtj3gGXLA20AFHLZaAqZzEGI/edit?gid=0#gid=0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>Gestion de Clientes rutas, ciudades etc. de transporte particular</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Plataforma Venta Permuta Vehiculos</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>josegar-venpermutas.streamlit.app</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>jagt2024/Reservar/jjgt_venpermuta/app.py</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>streamlit</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>1D3AjIC_SMrYPzdfl6eNct0xu9yJlGBZWblN91yEGUYw/edit?gid=1575378370#gid=1575378370</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>App para la venta y pernmuta de vehiculos</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>AplicaionparaAbogadosp</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>josegar-abogados.streamlit.app</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>jagt2024/Reservar/ main-abo.py</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>jagt2024/Reservar/main-abo.py</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>streamlit</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>1N_nVB02dmzHTCNkufR2fmuRBY7Lf8FUbhTpqAEWRWF4/edit?gid=0#gid=0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>Gestion   de   cssos y clinte   de abogados</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
@@ -1127,17 +1176,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1158,7 +1207,7 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>Fecha Backup</t>
+          <t>Fecha</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
@@ -1168,7 +1217,7 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>Tamaño KB</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
@@ -1184,356 +1233,145 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AplicaionparaAbogadosp</t>
+          <t>Plataforma Venta Permuta Vehiculos</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-21T11:55:30.949115</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
+          <t>2026-03-21T14:29:06.529587</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8.789999999999999</v>
+        <v>128.5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Google Drive / JAGT-Hosting / hosting-jagt.xlsx</t>
+          <t>Google Drive / hosting-jagt</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Backup automático diario — estructura hosting</t>
+          <t>Backup manual desde panel</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plataforma Venta Permuta Vehiculos</t>
+          <t>Admon Conjuntos</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-21T11:55:27.927258</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
+          <t>2026-03-21T11:11:20.734493</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8.789999999999999</v>
+        <v>256</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Google Drive / JAGT-Hosting / hosting-jagt.xlsx</t>
+          <t>Google Drive / hosting-jagt</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Backup automático diario — estructura hosting</t>
+          <t>Backup manual desde panel</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plataforma Autos Particulares</t>
+          <t>Agenda Empresa serv.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-21T11:55:25.473406</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
+          <t>2026-03-21T11:01:03.298746</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8.789999999999999</v>
+        <v>128.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Google Drive / JAGT-Hosting / hosting-jagt.xlsx</t>
+          <t>Google Drive / hosting-jagt</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Backup automático diario — estructura hosting</t>
+          <t>Backup manual desde panel</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Clinica de Psicologia</t>
+          <t>JAGT Landing Page</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-21T11:55:24.468521</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
+          <t>2026-03-21T10:55:27.046758</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>8.789999999999999</v>
+        <v>256</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Google Drive / JAGT-Hosting / hosting-jagt.xlsx</t>
+          <t>Local DB</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Backup automático diario — estructura hosting</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Productos de Aseo</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-03-21T11:55:21.450651</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>8.789999999999999</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Google Drive / JAGT-Hosting / hosting-jagt.xlsx</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Backup automático diario — estructura hosting</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Panel Hosting</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-03-21T11:55:19.583616</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>8.789999999999999</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Google Drive / JAGT-Hosting / hosting-jagt.xlsx</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Backup automático diario — estructura hosting</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Admon Conjuntos</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-03-21T11:55:18.439794</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>8.789999999999999</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Google Drive / JAGT-Hosting / hosting-jagt.xlsx</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Backup automático diario — estructura hosting</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Agenda Empresa serv.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-03-21T11:55:17.574887</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>8.789999999999999</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Google Drive / JAGT-Hosting / hosting-jagt.xlsx</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Backup automático diario — estructura hosting</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>JAGT Landing Page</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-03-21T11:55:16.096834</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>8.789999999999999</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Google Drive / JAGT-Hosting / hosting-jagt.xlsx</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Backup automático diario — estructura hosting</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-03-21T11:55:14.812774</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>8.789999999999999</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Google Drive / JAGT-Hosting / hosting-jagt_backup_20260321_115448.xlsx</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Backup automático de 'hosting-jagt.xlsx' → 'hosting-jagt_backup_20260321_115448.xlsx'</t>
+          <t>Backup manual desde panel</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1509,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
     </row>

--- a/hosting/scripts/hosting-jagt.xlsx
+++ b/hosting/scripts/hosting-jagt.xlsx
@@ -53,7 +53,8 @@
       <color rgb="0010B981"/>
     </font>
     <font>
-      <color rgb="0010B981"/>
+      <b val="1"/>
+      <color rgb="00EF4444"/>
     </font>
   </fonts>
   <fills count="4">
@@ -86,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -94,8 +95,14 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,7 +472,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -567,7 +574,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>hosting_jagt.db</t>
+          <t>hosting_jagt.db (SQLite3)</t>
         </is>
       </c>
     </row>
@@ -579,7 +586,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2026-03-22 10:19:14</t>
+          <t>2026-03-22 14:37:16</t>
         </is>
       </c>
     </row>
@@ -597,20 +604,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="35" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -631,7 +637,7 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>Repo</t>
+          <t>Repo GitHub</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
@@ -651,515 +657,465 @@
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
-          <t>Frec</t>
+          <t>Frecuencia</t>
         </is>
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>Sheet ID</t>
+          <t>Descripción</t>
         </is>
       </c>
       <c r="J1" s="4" t="inlineStr">
         <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
           <t>Creada</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>JAGT Landing Page</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>josegart.streamlit.app</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>jagt2024/Reservar/pagina_web/jagt_landing.py</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>streamlit</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>16F7ncXQJVmUJMMsl1So8FdfRZX9Vlo_nHkL9pWULjSE/edit?gid=855258571#gid=855258571</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>Página web personal JAGT</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Agenda Empresa serv.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>josegart-agenda.streamlit.app</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>jagt2024/Reservar/Agenda/main_agenda.py</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>streamlit</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>13UqQN6VXO9vTDIhyAEON9Qf5SD-1tgGgDA-Zo38udso/edit?gid=163711379#gid=163711379</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Empresas de Servicios temporales</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Admon Conjuntos</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>josegart-conjuntos.streamlit.app</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>jagt2024/Reservar/Admon-Conjuntos/main_conjunto_cb.py</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>streamlit</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>1UqCfVwwQfAkzRHG4_YCX8BD3Xl95KB7qvwjZNXWkzKw/edit?gid=210975473#gid=210975473</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Sistema de administracion de conjuntos</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Panel Hosting</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>josegart-hosting.streamlit.app</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>jagt2024/Reservar/hosting/app.py</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>streamlit</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>1PXLNO-QL4bIqD_R4awEK71OunP7AUCysSZ5nWk4PqB0/edit?gid=1502391982#gid=1502391982</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Panel de control del hosting</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Productos de Aseo</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>josegart-claridad.streamlit.app</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>jagt2024/Reservar/claridad/main_emp_cld.py</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>streamlit</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>1SKW_Tmk2H2V4OGKaELmVsvRmEe2x8UJJAKPdpTRimNg/edit?gid=1910642720#gid=1910642720</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>Venta de productos de aseo</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Clinica de Psicologia</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>josegart-clinica.streamlit.app</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>jagt2024/Reservar/Clinica-Amor/main_emp_amo.py</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>streamlit</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>19FjdgHOjwbrilbhBuNhn7cFwTzKqy7cabh1Nc6QQCv4/edit?gid=0#gid=0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Gestion Clientes e Historias Clinicas</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Plataforma Autos Particulares</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>josegar-autos.streamlit.app</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>jagt2024/Reservar/DP-Andres/main_emp_dp.py</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>streamlit</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>18Xzq0almiDk740OyywLTtj3gGXLA20AFHLZaAqZzEGI/edit?gid=0#gid=0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>Gestion de Clientes rutas, ciudades etc. de transporte particular</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Plataforma Venta Permuta Vehiculos</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>josegar-venpermutas.streamlit.app</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>jagt2024/Reservar/jjgt_venpermuta/app.py</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>streamlit</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>1D3AjIC_SMrYPzdfl6eNct0xu9yJlGBZWblN91yEGUYw/edit?gid=1575378370#gid=1575378370</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>App para la venta y pernmuta de vehiculos</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>AplicaionparaAbogadosp</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>josegar-abogados.streamlit.app</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>jagt2024/Reservar/main-abo.py</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>streamlit</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>1N_nVB02dmzHTCNkufR2fmuRBY7Lf8FUbhTpqAEWRWF4/edit?gid=0#gid=0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Gestion   de   cssos y clinte   de abogados</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
@@ -1176,17 +1132,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1207,7 +1163,7 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>Fecha</t>
+          <t>Fecha Backup</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
@@ -1217,7 +1173,7 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>Tamaño KB</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
@@ -1233,143 +1189,2411 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plataforma Venta Permuta Vehiculos</t>
+          <t>AplicaionparaAbogadosp</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-21T14:29:06.529587</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>success</t>
+          <t>2026-03-22T14:32:09.916343</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>128.5</v>
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Google Drive / hosting-jagt</t>
+          <t>Google Drive / JAGT-Hosting / AplicaionparaAbogadosp_backup_20260322_142704.xlsx</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Backup manual desde panel</t>
+          <t>Error exportando Sheet 1N_nVB02dmzHTCNkufR2fmuRBY7Lf8FUbhTpqAEWRWF4: [WinError 10060] Se produjo un error durante el intento de conexión ya que la parte conectada no respondió adecuadamente tras un periodo de tiempo, o bien se produjo un error en la conexión establecid</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Admon Conjuntos</t>
+          <t>Plataforma Venta Permuta Vehiculos</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-21T11:11:20.734493</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>success</t>
+          <t>2026-03-22T14:31:48.243097</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Google Drive / hosting-jagt</t>
+          <t>Google Drive / JAGT-Hosting / Plataforma_Venta_Permuta_Vehiculos_backup_20260322_142704.xlsx</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Backup manual desde panel</t>
+          <t>Error exportando Sheet 1D3AjIC_SMrYPzdfl6eNct0xu9yJlGBZWblN91yEGUYw: [SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1000)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Agenda Empresa serv.</t>
+          <t>Plataforma Autos Particulares</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-21T11:01:03.298746</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>success</t>
+          <t>2026-03-22T14:31:30.507390</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>128.5</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Google Drive / hosting-jagt</t>
+          <t>Google Drive / JAGT-Hosting / Plataforma_Autos_Particulares_backup_20260322_142704.xlsx</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Backup manual desde panel</t>
+          <t>Error exportando Sheet 18Xzq0almiDk740OyywLTtj3gGXLA20AFHLZaAqZzEGI: Unable to find the server at www.googleapis.com</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Clinica de Psicologia</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-03-22T14:31:18.744256</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Google Drive / JAGT-Hosting / Clinica_de_Psicologia_backup_20260322_142704.xlsx</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Error exportando Sheet 19FjdgHOjwbrilbhBuNhn7cFwTzKqy7cabh1Nc6QQCv4: Unable to find the server at www.googleapis.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>63</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Productos de Aseo</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-03-22T14:30:45.272483</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Google Drive / JAGT-Hosting / Productos_de_Aseo_backup_20260322_142704.xlsx</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Error exportando Sheet 1SKW_Tmk2H2V4OGKaELmVsvRmEe2x8UJJAKPdpTRimNg: [WinError 10060] Se produjo un error durante el intento de conexión ya que la parte conectada no respondió adecuadamente tras un periodo de tiempo, o bien se produjo un error en la conexión establecid</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Panel Hosting</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-03-22T14:30:23.592177</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Google Drive / JAGT-Hosting / Panel_Hosting_backup_20260322_142704.xlsx</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Error exportando Sheet 1PXLNO-QL4bIqD_R4awEK71OunP7AUCysSZ5nWk4PqB0: [SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>61</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Admon Conjuntos</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-03-22T14:29:45.751561</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Google Drive / JAGT-Hosting / Admon_Conjuntos_backup_20260322_142704.xlsx</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Error exportando Sheet 1UqCfVwwQfAkzRHG4_YCX8BD3Xl95KB7qvwjZNXWkzKw: [WinError 10060] Se produjo un error durante el intento de conexión ya que la parte conectada no respondió adecuadamente tras un periodo de tiempo, o bien se produjo un error en la conexión establecid</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>60</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Agenda Empresa serv.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-03-22T14:29:24.207990</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Google Drive / JAGT-Hosting / Agenda_Empresa_serv._backup_20260322_142704.xlsx</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Error exportando Sheet 13UqQN6VXO9vTDIhyAEON9Qf5SD-1tgGgDA-Zo38udso: [SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>59</v>
+      </c>
+      <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>JAGT Landing Page</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-03-22T14:29:07.677418</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Google Drive / JAGT-Hosting / JAGT_Landing_Page_backup_20260322_142704.xlsx</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Error exportando Sheet 16F7ncXQJVmUJMMsl1So8FdfRZX9Vlo_nHkL9pWULjSE: Unable to find the server at oauth2.googleapis.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>58</v>
+      </c>
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AplicaionparaAbogadosp</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:57:47.785818</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/AplicaionparaAbogadosp_backup_20260322_115045.xlsx</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 1N_nVB02dmzHTCNkufR2fmuRBY7Lf8FUbhTpqAEWRWF4/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>57</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Plataforma Venta Permuta Vehiculos</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:57:46.297719</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/Plataforma_Venta_Permuta_Vehiculos_backup_20260322_115045.xlsx</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 1D3AjIC_SMrYPzdfl6eNct0xu9yJlGBZWblN91yEGUYw/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>56</v>
+      </c>
+      <c r="B13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Plataforma Autos Particulares</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:57:44.900215</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/Plataforma_Autos_Particulares_backup_20260322_115045.xlsx</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 18Xzq0almiDk740OyywLTtj3gGXLA20AFHLZaAqZzEGI/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>55</v>
+      </c>
+      <c r="B14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Clinica de Psicologia</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:57:43.295756</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/Clinica_de_Psicologia_backup_20260322_115045.xlsx</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 19FjdgHOjwbrilbhBuNhn7cFwTzKqy7cabh1Nc6QQCv4/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>54</v>
+      </c>
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Productos de Aseo</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:57:35.524436</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/Productos_de_Aseo_backup_20260322_115045.xlsx</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 1SKW_Tmk2H2V4OGKaELmVsvRmEe2x8UJJAKPdpTRimNg/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>53</v>
+      </c>
+      <c r="B16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Panel Hosting</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:56:34.701278</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/Panel_Hosting_backup_20260322_115045.xlsx</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 1PXLNO-QL4bIqD_R4awEK71OunP7AUCysSZ5nWk4PqB0/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>52</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Admon Conjuntos</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:56:14.535491</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/Admon_Conjuntos_backup_20260322_115045.xlsx</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 1UqCfVwwQfAkzRHG4_YCX8BD3Xl95KB7qvwjZNXWkzKw/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>51</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Agenda Empresa serv.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:56:10.031155</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/Agenda_Empresa_serv._backup_20260322_115045.xlsx</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 13UqQN6VXO9vTDIhyAEON9Qf5SD-1tgGgDA-Zo38udso/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>50</v>
+      </c>
+      <c r="B19" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>JAGT Landing Page</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:56:07.078407</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/JAGT_Landing_Page_backup_20260322_115045.xlsx</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 16F7ncXQJVmUJMMsl1So8FdfRZX9Vlo_nHkL9pWULjSE/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>49</v>
+      </c>
+      <c r="B20" t="n">
+        <v>9</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AplicaionparaAbogadosp</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:56:05.444943</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>12</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — AplicaionparaAbogadosp</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>48</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Plataforma Venta Permuta Vehiculos</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:56:04.793951</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>12</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — Plataforma Venta Permuta Vehiculos</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>47</v>
+      </c>
+      <c r="B22" t="n">
+        <v>7</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Plataforma Autos Particulares</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:56:04.250365</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>12</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — Plataforma Autos Particulares</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>46</v>
+      </c>
+      <c r="B23" t="n">
+        <v>6</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Clinica de Psicologia</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:56:03.217610</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>12</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — Clinica de Psicologia</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>45</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Productos de Aseo</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:56:02.615341</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>12</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — Productos de Aseo</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>44</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Panel Hosting</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:56:02.088118</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>12</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — Panel Hosting</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>43</v>
+      </c>
+      <c r="B26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Admon Conjuntos</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:56:01.220759</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>12</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — Admon Conjuntos</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>42</v>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Agenda Empresa serv.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:55:59.529277</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>12</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — Agenda Empresa serv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>41</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>JAGT Landing Page</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:55:58.592491</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>12</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — JAGT Landing Page</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>40</v>
+      </c>
+      <c r="B29" t="n">
+        <v>9</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AplicaionparaAbogadosp</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:20:22.694929</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/AplicaionparaAbogadosp_backup_20260322_111842.xlsx</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 1N_nVB02dmzHTCNkufR2fmuRBY7Lf8FUbhTpqAEWRWF4/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>39</v>
+      </c>
+      <c r="B30" t="n">
+        <v>8</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Plataforma Venta Permuta Vehiculos</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:20:21.032457</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/Plataforma_Venta_Permuta_Vehiculos_backup_20260322_111842.xlsx</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 1D3AjIC_SMrYPzdfl6eNct0xu9yJlGBZWblN91yEGUYw/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>38</v>
+      </c>
+      <c r="B31" t="n">
+        <v>7</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Plataforma Autos Particulares</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:20:19.311865</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/Plataforma_Autos_Particulares_backup_20260322_111842.xlsx</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 18Xzq0almiDk740OyywLTtj3gGXLA20AFHLZaAqZzEGI/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>37</v>
+      </c>
+      <c r="B32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Clinica de Psicologia</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:20:17.047870</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/Clinica_de_Psicologia_backup_20260322_111842.xlsx</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 19FjdgHOjwbrilbhBuNhn7cFwTzKqy7cabh1Nc6QQCv4/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>36</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Productos de Aseo</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:20:15.596872</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/Productos_de_Aseo_backup_20260322_111842.xlsx</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 1SKW_Tmk2H2V4OGKaELmVsvRmEe2x8UJJAKPdpTRimNg/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>35</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Panel Hosting</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:20:14.171873</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/Panel_Hosting_backup_20260322_111842.xlsx</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 1PXLNO-QL4bIqD_R4awEK71OunP7AUCysSZ5nWk4PqB0/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Admon Conjuntos</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:20:11.087774</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/Admon_Conjuntos_backup_20260322_111842.xlsx</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 1UqCfVwwQfAkzRHG4_YCX8BD3Xl95KB7qvwjZNXWkzKw/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Agenda Empresa serv.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:20:09.931210</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/Agenda_Empresa_serv._backup_20260322_111842.xlsx</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 13UqQN6VXO9vTDIhyAEON9Qf5SD-1tgGgDA-Zo38udso/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>JAGT Landing Page</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:20:08.067222</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/JAGT_Landing_Page_backup_20260322_111842.xlsx</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 16F7ncXQJVmUJMMsl1So8FdfRZX9Vlo_nHkL9pWULjSE/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>31</v>
+      </c>
+      <c r="B38" t="n">
+        <v>9</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AplicaionparaAbogadosp</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:20:05.063698</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — AplicaionparaAbogadosp</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>30</v>
+      </c>
+      <c r="B39" t="n">
+        <v>8</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Plataforma Venta Permuta Vehiculos</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:20:04.302423</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — Plataforma Venta Permuta Vehiculos</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>29</v>
+      </c>
+      <c r="B40" t="n">
+        <v>7</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Plataforma Autos Particulares</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:20:03.053507</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — Plataforma Autos Particulares</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>28</v>
+      </c>
+      <c r="B41" t="n">
+        <v>6</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Clinica de Psicologia</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:20:02.385674</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — Clinica de Psicologia</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>27</v>
+      </c>
+      <c r="B42" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Productos de Aseo</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:20:01.706698</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — Productos de Aseo</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>26</v>
+      </c>
+      <c r="B43" t="n">
+        <v>4</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Panel Hosting</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:20:00.720728</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — Panel Hosting</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>25</v>
+      </c>
+      <c r="B44" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Admon Conjuntos</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:19:59.672243</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — Admon Conjuntos</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>24</v>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Agenda Empresa serv.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:19:58.362322</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — Agenda Empresa serv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>23</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>JAGT Landing Page</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:19:57.624747</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — JAGT Landing Page</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>22</v>
+      </c>
+      <c r="B47" t="n">
+        <v>9</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AplicaionparaAbogadosp</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-03-22T10:21:15.155904</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/AplicaionparaAbogadosp_backup_20260322_101832.xlsx</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 1N_nVB02dmzHTCNkufR2fmuRBY7Lf8FUbhTpqAEWRWF4/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>21</v>
+      </c>
+      <c r="B48" t="n">
+        <v>8</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Plataforma Venta Permuta Vehiculos</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-03-22T10:21:12.354664</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/Plataforma_Venta_Permuta_Vehiculos_backup_20260322_101832.xlsx</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 1D3AjIC_SMrYPzdfl6eNct0xu9yJlGBZWblN91yEGUYw/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>20</v>
+      </c>
+      <c r="B49" t="n">
+        <v>7</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Plataforma Autos Particulares</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-03-22T10:21:09.693330</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/Plataforma_Autos_Particulares_backup_20260322_101832.xlsx</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 18Xzq0almiDk740OyywLTtj3gGXLA20AFHLZaAqZzEGI/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>19</v>
+      </c>
+      <c r="B50" t="n">
+        <v>6</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Clinica de Psicologia</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-03-22T10:21:07.041268</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/Clinica_de_Psicologia_backup_20260322_101832.xlsx</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 19FjdgHOjwbrilbhBuNhn7cFwTzKqy7cabh1Nc6QQCv4/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>18</v>
+      </c>
+      <c r="B51" t="n">
+        <v>5</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Productos de Aseo</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-03-22T10:21:04.189600</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/Productos_de_Aseo_backup_20260322_101832.xlsx</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 1SKW_Tmk2H2V4OGKaELmVsvRmEe2x8UJJAKPdpTRimNg/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>17</v>
+      </c>
+      <c r="B52" t="n">
+        <v>4</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Panel Hosting</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-03-22T10:21:01.269981</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/Panel_Hosting_backup_20260322_101832.xlsx</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 1PXLNO-QL4bIqD_R4awEK71OunP7AUCysSZ5nWk4PqB0/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>16</v>
+      </c>
+      <c r="B53" t="n">
+        <v>3</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Admon Conjuntos</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-03-22T10:20:59.136831</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/Admon_Conjuntos_backup_20260322_101832.xlsx</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 1UqCfVwwQfAkzRHG4_YCX8BD3Xl95KB7qvwjZNXWkzKw/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>15</v>
+      </c>
+      <c r="B54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Agenda Empresa serv.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-03-22T10:20:55.590849</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/Agenda_Empresa_serv._backup_20260322_101832.xlsx</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 13UqQN6VXO9vTDIhyAEON9Qf5SD-1tgGgDA-Zo38udso/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>14</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>JAGT Landing Page</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-03-22T10:20:52.430736</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/JAGT_Landing_Page_backup_20260322_101832.xlsx</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>ERROR exportando Sheet 16F7ncXQJVmUJMMsl1So8FdfRZX9Vlo_nHkL9pWULjSE/edit — verifica permisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>13</v>
+      </c>
+      <c r="B56" t="n">
+        <v>9</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AplicaionparaAbogadosp</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-03-22T10:20:48.650981</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — AplicaionparaAbogadosp</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>12</v>
+      </c>
+      <c r="B57" t="n">
+        <v>8</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Plataforma Venta Permuta Vehiculos</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-03-22T10:20:44.187288</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — Plataforma Venta Permuta Vehiculos</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>11</v>
+      </c>
+      <c r="B58" t="n">
+        <v>7</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Plataforma Autos Particulares</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-03-22T10:20:41.744104</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — Plataforma Autos Particulares</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>10</v>
+      </c>
+      <c r="B59" t="n">
+        <v>6</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Clinica de Psicologia</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-03-22T10:20:39.360604</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — Clinica de Psicologia</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>9</v>
+      </c>
+      <c r="B60" t="n">
+        <v>5</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Productos de Aseo</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-03-22T10:20:38.428439</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — Productos de Aseo</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>8</v>
+      </c>
+      <c r="B61" t="n">
+        <v>4</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Panel Hosting</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-03-22T10:20:37.219042</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — Panel Hosting</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>7</v>
+      </c>
+      <c r="B62" t="n">
+        <v>3</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Admon Conjuntos</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-03-22T10:20:36.528699</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — Admon Conjuntos</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>6</v>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Agenda Empresa serv.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-03-22T10:20:34.796287</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — Agenda Empresa serv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>5</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>JAGT Landing Page</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-03-22T10:20:34.113591</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Estructura hosting exportada — JAGT Landing Page</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>4</v>
+      </c>
+      <c r="B65" t="n">
+        <v>8</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Plataforma Venta Permuta Vehiculos</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-03-21T14:29:06.529587</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Google Drive / hosting-jagt</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Backup manual desde panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>3</v>
+      </c>
+      <c r="B66" t="n">
+        <v>3</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Admon Conjuntos</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-03-21T11:11:20.734493</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>256</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Google Drive / hosting-jagt</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Backup manual desde panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2</v>
+      </c>
+      <c r="B67" t="n">
+        <v>2</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Agenda Empresa serv.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-03-21T11:01:03.298746</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Google Drive / hosting-jagt</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Backup manual desde panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>1</v>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>JAGT Landing Page</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
         <is>
           <t>2026-03-21T10:55:27.046758</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E68" s="8" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F68" t="n">
         <v>256</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Local DB</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>Backup manual desde panel</t>
         </is>

--- a/hosting/scripts/hosting-jagt.xlsx
+++ b/hosting/scripts/hosting-jagt.xlsx
@@ -101,8 +101,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -514,7 +514,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>github.com/jagt2024/Reservar/</t>
+          <t>github.com/jagt2024/reservar/</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2026-03-22 14:37:16</t>
+          <t>2026-03-23 11:15:46</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>jagt2024/Reservar/pagina_web/jagt_landing.py</t>
+          <t>jagt2024/reservar/pagina_web/jagt_landing.py</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>jagt2024/Reservar/Agenda/main_agenda.py</t>
+          <t>jagt2024/reservar/Agenda/main_agenda.py</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>jagt2024/Reservar/Admon-Conjuntos/main_conjunto_cb.py</t>
+          <t>jagt2024/reservar/Admon-Conjuntos/main_conjunto_cb.py</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>jagt2024/Reservar/hosting/app.py</t>
+          <t>jagt2024/reservar/hosting/app.py</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>jagt2024/Reservar/claridad/main_emp_cld.py</t>
+          <t>jagt2024/reservar/claridad/main_emp_cld.py</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>jagt2024/Reservar/Clinica-Amor/main_emp_amo.py</t>
+          <t>jagt2024/reservar/Clinica-Amor/main_emp_amo.py</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>jagt2024/Reservar/DP-Andres/main_emp_dp.py</t>
+          <t>jagt2024/reservar/DP-Andres/main_emp_dp.py</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>jagt2024/Reservar/jjgt_venpermuta/app.py</t>
+          <t>jagt2024/reservar/jjgt_venpermuta/app.py</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>jagt2024/Reservar/main-abo.py</t>
+          <t>jagt2024/reservar/main-abo.py</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1132,7 +1132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1189,130 +1189,130 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AplicaionparaAbogadosp</t>
+          <t>Agenda Empresa serv.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-22T14:32:09.916343</t>
+          <t>2026-03-22T11:37:37.909064</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>128.5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Google Drive / JAGT-Hosting / AplicaionparaAbogadosp_backup_20260322_142704.xlsx</t>
+          <t>Google Drive / hosting-jagt</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Error exportando Sheet 1N_nVB02dmzHTCNkufR2fmuRBY7Lf8FUbhTpqAEWRWF4: [WinError 10060] Se produjo un error durante el intento de conexión ya que la parte conectada no respondió adecuadamente tras un periodo de tiempo, o bien se produjo un error en la conexión establecid</t>
+          <t>Backup manual desde panel</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plataforma Venta Permuta Vehiculos</t>
+          <t>JAGT Landing Page</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-22T14:31:48.243097</t>
+          <t>2026-03-22T11:34:57.962045</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Google Drive / JAGT-Hosting / Plataforma_Venta_Permuta_Vehiculos_backup_20260322_142704.xlsx</t>
+          <t>Google Drive / hosting-jagt</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Error exportando Sheet 1D3AjIC_SMrYPzdfl6eNct0xu9yJlGBZWblN91yEGUYw: [SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1000)</t>
+          <t>Backup manual desde panel</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plataforma Autos Particulares</t>
+          <t>JAGT Landing Page</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-22T14:31:30.507390</t>
+          <t>2026-03-22T11:28:43.122250</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>128.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Google Drive / JAGT-Hosting / Plataforma_Autos_Particulares_backup_20260322_142704.xlsx</t>
+          <t>Google Drive / hosting-jagt</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Error exportando Sheet 18Xzq0almiDk740OyywLTtj3gGXLA20AFHLZaAqZzEGI: Unable to find the server at www.googleapis.com</t>
+          <t>Backup manual desde panel</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Clinica de Psicologia</t>
+          <t>AplicaionparaAbogadosp</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-22T14:31:18.744256</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
+          <t>2026-03-22T10:21:15.155904</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -1322,33 +1322,33 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Google Drive / JAGT-Hosting / Clinica_de_Psicologia_backup_20260322_142704.xlsx</t>
+          <t>Google Drive/JAGT-Hosting/AplicaionparaAbogadosp_backup_20260322_101832.xlsx</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Error exportando Sheet 19FjdgHOjwbrilbhBuNhn7cFwTzKqy7cabh1Nc6QQCv4: Unable to find the server at www.googleapis.com</t>
+          <t>ERROR exportando Sheet 1N_nVB02dmzHTCNkufR2fmuRBY7Lf8FUbhTpqAEWRWF4/edit — verifica permisos</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Productos de Aseo</t>
+          <t>Plataforma Venta Permuta Vehiculos</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-22T14:30:45.272483</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
+          <t>2026-03-22T10:21:12.354664</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -1358,33 +1358,33 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Google Drive / JAGT-Hosting / Productos_de_Aseo_backup_20260322_142704.xlsx</t>
+          <t>Google Drive/JAGT-Hosting/Plataforma_Venta_Permuta_Vehiculos_backup_20260322_101832.xlsx</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Error exportando Sheet 1SKW_Tmk2H2V4OGKaELmVsvRmEe2x8UJJAKPdpTRimNg: [WinError 10060] Se produjo un error durante el intento de conexión ya que la parte conectada no respondió adecuadamente tras un periodo de tiempo, o bien se produjo un error en la conexión establecid</t>
+          <t>ERROR exportando Sheet 1D3AjIC_SMrYPzdfl6eNct0xu9yJlGBZWblN91yEGUYw/edit — verifica permisos</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Panel Hosting</t>
+          <t>Plataforma Autos Particulares</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-22T14:30:23.592177</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
+          <t>2026-03-22T10:21:09.693330</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -1394,33 +1394,33 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Google Drive / JAGT-Hosting / Panel_Hosting_backup_20260322_142704.xlsx</t>
+          <t>Google Drive/JAGT-Hosting/Plataforma_Autos_Particulares_backup_20260322_101832.xlsx</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Error exportando Sheet 1PXLNO-QL4bIqD_R4awEK71OunP7AUCysSZ5nWk4PqB0: [SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1000)</t>
+          <t>ERROR exportando Sheet 18Xzq0almiDk740OyywLTtj3gGXLA20AFHLZaAqZzEGI/edit — verifica permisos</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Admon Conjuntos</t>
+          <t>Clinica de Psicologia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-22T14:29:45.751561</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
+          <t>2026-03-22T10:21:07.041268</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -1430,33 +1430,33 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Google Drive / JAGT-Hosting / Admon_Conjuntos_backup_20260322_142704.xlsx</t>
+          <t>Google Drive/JAGT-Hosting/Clinica_de_Psicologia_backup_20260322_101832.xlsx</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Error exportando Sheet 1UqCfVwwQfAkzRHG4_YCX8BD3Xl95KB7qvwjZNXWkzKw: [WinError 10060] Se produjo un error durante el intento de conexión ya que la parte conectada no respondió adecuadamente tras un periodo de tiempo, o bien se produjo un error en la conexión establecid</t>
+          <t>ERROR exportando Sheet 19FjdgHOjwbrilbhBuNhn7cFwTzKqy7cabh1Nc6QQCv4/edit — verifica permisos</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Agenda Empresa serv.</t>
+          <t>Productos de Aseo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-22T14:29:24.207990</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
+          <t>2026-03-22T10:21:04.189600</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -1466,33 +1466,33 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Google Drive / JAGT-Hosting / Agenda_Empresa_serv._backup_20260322_142704.xlsx</t>
+          <t>Google Drive/JAGT-Hosting/Productos_de_Aseo_backup_20260322_101832.xlsx</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Error exportando Sheet 13UqQN6VXO9vTDIhyAEON9Qf5SD-1tgGgDA-Zo38udso: [SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1000)</t>
+          <t>ERROR exportando Sheet 1SKW_Tmk2H2V4OGKaELmVsvRmEe2x8UJJAKPdpTRimNg/edit — verifica permisos</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JAGT Landing Page</t>
+          <t>Panel Hosting</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-22T14:29:07.677418</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
+          <t>2026-03-22T10:21:01.269981</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -1502,33 +1502,33 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Google Drive / JAGT-Hosting / JAGT_Landing_Page_backup_20260322_142704.xlsx</t>
+          <t>Google Drive/JAGT-Hosting/Panel_Hosting_backup_20260322_101832.xlsx</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Error exportando Sheet 16F7ncXQJVmUJMMsl1So8FdfRZX9Vlo_nHkL9pWULjSE: Unable to find the server at oauth2.googleapis.com</t>
+          <t>ERROR exportando Sheet 1PXLNO-QL4bIqD_R4awEK71OunP7AUCysSZ5nWk4PqB0/edit — verifica permisos</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AplicaionparaAbogadosp</t>
+          <t>Admon Conjuntos</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-22T11:57:47.785818</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
+          <t>2026-03-22T10:20:59.136831</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Google Drive/JAGT-Hosting/AplicaionparaAbogadosp_backup_20260322_115045.xlsx</t>
+          <t>Google Drive/JAGT-Hosting/Admon_Conjuntos_backup_20260322_101832.xlsx</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ERROR exportando Sheet 1N_nVB02dmzHTCNkufR2fmuRBY7Lf8FUbhTpqAEWRWF4/edit — verifica permisos</t>
+          <t>ERROR exportando Sheet 1UqCfVwwQfAkzRHG4_YCX8BD3Xl95KB7qvwjZNXWkzKw/edit — verifica permisos</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plataforma Venta Permuta Vehiculos</t>
+          <t>Agenda Empresa serv.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-22T11:57:46.297719</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
+          <t>2026-03-22T10:20:55.590849</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -1574,33 +1574,33 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Google Drive/JAGT-Hosting/Plataforma_Venta_Permuta_Vehiculos_backup_20260322_115045.xlsx</t>
+          <t>Google Drive/JAGT-Hosting/Agenda_Empresa_serv._backup_20260322_101832.xlsx</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ERROR exportando Sheet 1D3AjIC_SMrYPzdfl6eNct0xu9yJlGBZWblN91yEGUYw/edit — verifica permisos</t>
+          <t>ERROR exportando Sheet 13UqQN6VXO9vTDIhyAEON9Qf5SD-1tgGgDA-Zo38udso/edit — verifica permisos</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plataforma Autos Particulares</t>
+          <t>JAGT Landing Page</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-22T11:57:44.900215</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
+          <t>2026-03-22T10:20:52.430736</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -1610,255 +1610,255 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Google Drive/JAGT-Hosting/Plataforma_Autos_Particulares_backup_20260322_115045.xlsx</t>
+          <t>Google Drive/JAGT-Hosting/JAGT_Landing_Page_backup_20260322_101832.xlsx</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>ERROR exportando Sheet 18Xzq0almiDk740OyywLTtj3gGXLA20AFHLZaAqZzEGI/edit — verifica permisos</t>
+          <t>ERROR exportando Sheet 16F7ncXQJVmUJMMsl1So8FdfRZX9Vlo_nHkL9pWULjSE/edit — verifica permisos</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Clinica de Psicologia</t>
+          <t>AplicaionparaAbogadosp</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-22T11:57:43.295756</t>
+          <t>2026-03-22T10:20:48.650981</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>9.59</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Google Drive/JAGT-Hosting/Clinica_de_Psicologia_backup_20260322_115045.xlsx</t>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ERROR exportando Sheet 19FjdgHOjwbrilbhBuNhn7cFwTzKqy7cabh1Nc6QQCv4/edit — verifica permisos</t>
+          <t>Estructura hosting exportada — AplicaionparaAbogadosp</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Productos de Aseo</t>
+          <t>Plataforma Venta Permuta Vehiculos</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-22T11:57:35.524436</t>
+          <t>2026-03-22T10:20:44.187288</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>9.59</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Google Drive/JAGT-Hosting/Productos_de_Aseo_backup_20260322_115045.xlsx</t>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>ERROR exportando Sheet 1SKW_Tmk2H2V4OGKaELmVsvRmEe2x8UJJAKPdpTRimNg/edit — verifica permisos</t>
+          <t>Estructura hosting exportada — Plataforma Venta Permuta Vehiculos</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Panel Hosting</t>
+          <t>Plataforma Autos Particulares</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-22T11:56:34.701278</t>
+          <t>2026-03-22T10:20:41.744104</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>9.59</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Google Drive/JAGT-Hosting/Panel_Hosting_backup_20260322_115045.xlsx</t>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ERROR exportando Sheet 1PXLNO-QL4bIqD_R4awEK71OunP7AUCysSZ5nWk4PqB0/edit — verifica permisos</t>
+          <t>Estructura hosting exportada — Plataforma Autos Particulares</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Admon Conjuntos</t>
+          <t>Clinica de Psicologia</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-22T11:56:14.535491</t>
+          <t>2026-03-22T10:20:39.360604</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>9.59</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Google Drive/JAGT-Hosting/Admon_Conjuntos_backup_20260322_115045.xlsx</t>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ERROR exportando Sheet 1UqCfVwwQfAkzRHG4_YCX8BD3Xl95KB7qvwjZNXWkzKw/edit — verifica permisos</t>
+          <t>Estructura hosting exportada — Clinica de Psicologia</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Agenda Empresa serv.</t>
+          <t>Productos de Aseo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-22T11:56:10.031155</t>
+          <t>2026-03-22T10:20:38.428439</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>9.59</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Google Drive/JAGT-Hosting/Agenda_Empresa_serv._backup_20260322_115045.xlsx</t>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ERROR exportando Sheet 13UqQN6VXO9vTDIhyAEON9Qf5SD-1tgGgDA-Zo38udso/edit — verifica permisos</t>
+          <t>Estructura hosting exportada — Productos de Aseo</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>JAGT Landing Page</t>
+          <t>Panel Hosting</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-22T11:56:07.078407</t>
+          <t>2026-03-22T10:20:37.219042</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>9.59</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Google Drive/JAGT-Hosting/JAGT_Landing_Page_backup_20260322_115045.xlsx</t>
+          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>ERROR exportando Sheet 16F7ncXQJVmUJMMsl1So8FdfRZX9Vlo_nHkL9pWULjSE/edit — verifica permisos</t>
+          <t>Estructura hosting exportada — Panel Hosting</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AplicaionparaAbogadosp</t>
+          <t>Admon Conjuntos</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-22T11:56:05.444943</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
+          <t>2026-03-22T10:20:36.528699</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>12</v>
+        <v>9.59</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1867,34 +1867,34 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Estructura hosting exportada — AplicaionparaAbogadosp</t>
+          <t>Estructura hosting exportada — Admon Conjuntos</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Plataforma Venta Permuta Vehiculos</t>
+          <t>Agenda Empresa serv.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-22T11:56:04.793951</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
+          <t>2026-03-22T10:20:34.796287</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>9.59</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1903,34 +1903,34 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Estructura hosting exportada — Plataforma Venta Permuta Vehiculos</t>
+          <t>Estructura hosting exportada — Agenda Empresa serv.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plataforma Autos Particulares</t>
+          <t>JAGT Landing Page</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-22T11:56:04.250365</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
+          <t>2026-03-22T10:20:34.113591</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>12</v>
+        <v>9.59</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1939,1661 +1939,149 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Estructura hosting exportada — Plataforma Autos Particulares</t>
+          <t>Estructura hosting exportada — JAGT Landing Page</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Clinica de Psicologia</t>
+          <t>Plataforma Venta Permuta Vehiculos</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-22T11:56:03.217610</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
+          <t>2026-03-21T14:29:06.529587</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>12</v>
+        <v>128.5</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+          <t>Google Drive / hosting-jagt</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Estructura hosting exportada — Clinica de Psicologia</t>
+          <t>Backup manual desde panel</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Productos de Aseo</t>
+          <t>Admon Conjuntos</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-22T11:56:02.615341</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
+          <t>2026-03-21T11:11:20.734493</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>12</v>
+        <v>256</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+          <t>Google Drive / hosting-jagt</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Estructura hosting exportada — Productos de Aseo</t>
+          <t>Backup manual desde panel</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Panel Hosting</t>
+          <t>Agenda Empresa serv.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-22T11:56:02.088118</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
+          <t>2026-03-21T11:01:03.298746</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>12</v>
+        <v>128.5</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+          <t>Google Drive / hosting-jagt</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Estructura hosting exportada — Panel Hosting</t>
+          <t>Backup manual desde panel</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Admon Conjuntos</t>
+          <t>JAGT Landing Page</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-22T11:56:01.220759</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
+          <t>2026-03-21T10:55:27.046758</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>12</v>
+        <v>256</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
+          <t>Local DB</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
-        <is>
-          <t>Estructura hosting exportada — Admon Conjuntos</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>42</v>
-      </c>
-      <c r="B27" t="n">
-        <v>2</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Agenda Empresa serv.</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-03-22T11:55:59.529277</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>12</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Estructura hosting exportada — Agenda Empresa serv.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>41</v>
-      </c>
-      <c r="B28" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>JAGT Landing Page</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-03-22T11:55:58.592491</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>12</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Estructura hosting exportada — JAGT Landing Page</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>40</v>
-      </c>
-      <c r="B29" t="n">
-        <v>9</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>AplicaionparaAbogadosp</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-03-22T11:20:22.694929</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/AplicaionparaAbogadosp_backup_20260322_111842.xlsx</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>ERROR exportando Sheet 1N_nVB02dmzHTCNkufR2fmuRBY7Lf8FUbhTpqAEWRWF4/edit — verifica permisos</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>39</v>
-      </c>
-      <c r="B30" t="n">
-        <v>8</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Plataforma Venta Permuta Vehiculos</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-03-22T11:20:21.032457</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/Plataforma_Venta_Permuta_Vehiculos_backup_20260322_111842.xlsx</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>ERROR exportando Sheet 1D3AjIC_SMrYPzdfl6eNct0xu9yJlGBZWblN91yEGUYw/edit — verifica permisos</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>38</v>
-      </c>
-      <c r="B31" t="n">
-        <v>7</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Plataforma Autos Particulares</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026-03-22T11:20:19.311865</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/Plataforma_Autos_Particulares_backup_20260322_111842.xlsx</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>ERROR exportando Sheet 18Xzq0almiDk740OyywLTtj3gGXLA20AFHLZaAqZzEGI/edit — verifica permisos</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>37</v>
-      </c>
-      <c r="B32" t="n">
-        <v>6</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Clinica de Psicologia</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026-03-22T11:20:17.047870</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/Clinica_de_Psicologia_backup_20260322_111842.xlsx</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>ERROR exportando Sheet 19FjdgHOjwbrilbhBuNhn7cFwTzKqy7cabh1Nc6QQCv4/edit — verifica permisos</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>36</v>
-      </c>
-      <c r="B33" t="n">
-        <v>5</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Productos de Aseo</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2026-03-22T11:20:15.596872</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/Productos_de_Aseo_backup_20260322_111842.xlsx</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>ERROR exportando Sheet 1SKW_Tmk2H2V4OGKaELmVsvRmEe2x8UJJAKPdpTRimNg/edit — verifica permisos</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>35</v>
-      </c>
-      <c r="B34" t="n">
-        <v>4</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Panel Hosting</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2026-03-22T11:20:14.171873</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/Panel_Hosting_backup_20260322_111842.xlsx</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>ERROR exportando Sheet 1PXLNO-QL4bIqD_R4awEK71OunP7AUCysSZ5nWk4PqB0/edit — verifica permisos</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="n">
-        <v>3</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Admon Conjuntos</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026-03-22T11:20:11.087774</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/Admon_Conjuntos_backup_20260322_111842.xlsx</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>ERROR exportando Sheet 1UqCfVwwQfAkzRHG4_YCX8BD3Xl95KB7qvwjZNXWkzKw/edit — verifica permisos</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" t="n">
-        <v>2</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Agenda Empresa serv.</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026-03-22T11:20:09.931210</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/Agenda_Empresa_serv._backup_20260322_111842.xlsx</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>ERROR exportando Sheet 13UqQN6VXO9vTDIhyAEON9Qf5SD-1tgGgDA-Zo38udso/edit — verifica permisos</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>32</v>
-      </c>
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>JAGT Landing Page</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2026-03-22T11:20:08.067222</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/JAGT_Landing_Page_backup_20260322_111842.xlsx</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>ERROR exportando Sheet 16F7ncXQJVmUJMMsl1So8FdfRZX9Vlo_nHkL9pWULjSE/edit — verifica permisos</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>31</v>
-      </c>
-      <c r="B38" t="n">
-        <v>9</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>AplicaionparaAbogadosp</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2026-03-22T11:20:05.063698</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Estructura hosting exportada — AplicaionparaAbogadosp</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>30</v>
-      </c>
-      <c r="B39" t="n">
-        <v>8</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Plataforma Venta Permuta Vehiculos</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2026-03-22T11:20:04.302423</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Estructura hosting exportada — Plataforma Venta Permuta Vehiculos</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>29</v>
-      </c>
-      <c r="B40" t="n">
-        <v>7</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Plataforma Autos Particulares</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2026-03-22T11:20:03.053507</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Estructura hosting exportada — Plataforma Autos Particulares</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>28</v>
-      </c>
-      <c r="B41" t="n">
-        <v>6</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Clinica de Psicologia</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2026-03-22T11:20:02.385674</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Estructura hosting exportada — Clinica de Psicologia</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>27</v>
-      </c>
-      <c r="B42" t="n">
-        <v>5</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Productos de Aseo</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2026-03-22T11:20:01.706698</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Estructura hosting exportada — Productos de Aseo</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>26</v>
-      </c>
-      <c r="B43" t="n">
-        <v>4</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Panel Hosting</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2026-03-22T11:20:00.720728</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Estructura hosting exportada — Panel Hosting</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>25</v>
-      </c>
-      <c r="B44" t="n">
-        <v>3</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Admon Conjuntos</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2026-03-22T11:19:59.672243</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Estructura hosting exportada — Admon Conjuntos</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>24</v>
-      </c>
-      <c r="B45" t="n">
-        <v>2</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Agenda Empresa serv.</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2026-03-22T11:19:58.362322</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Estructura hosting exportada — Agenda Empresa serv.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>23</v>
-      </c>
-      <c r="B46" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>JAGT Landing Page</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2026-03-22T11:19:57.624747</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Estructura hosting exportada — JAGT Landing Page</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>22</v>
-      </c>
-      <c r="B47" t="n">
-        <v>9</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>AplicaionparaAbogadosp</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2026-03-22T10:21:15.155904</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/AplicaionparaAbogadosp_backup_20260322_101832.xlsx</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>ERROR exportando Sheet 1N_nVB02dmzHTCNkufR2fmuRBY7Lf8FUbhTpqAEWRWF4/edit — verifica permisos</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>21</v>
-      </c>
-      <c r="B48" t="n">
-        <v>8</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Plataforma Venta Permuta Vehiculos</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2026-03-22T10:21:12.354664</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/Plataforma_Venta_Permuta_Vehiculos_backup_20260322_101832.xlsx</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>ERROR exportando Sheet 1D3AjIC_SMrYPzdfl6eNct0xu9yJlGBZWblN91yEGUYw/edit — verifica permisos</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>20</v>
-      </c>
-      <c r="B49" t="n">
-        <v>7</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Plataforma Autos Particulares</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2026-03-22T10:21:09.693330</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/Plataforma_Autos_Particulares_backup_20260322_101832.xlsx</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>ERROR exportando Sheet 18Xzq0almiDk740OyywLTtj3gGXLA20AFHLZaAqZzEGI/edit — verifica permisos</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>19</v>
-      </c>
-      <c r="B50" t="n">
-        <v>6</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Clinica de Psicologia</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2026-03-22T10:21:07.041268</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/Clinica_de_Psicologia_backup_20260322_101832.xlsx</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>ERROR exportando Sheet 19FjdgHOjwbrilbhBuNhn7cFwTzKqy7cabh1Nc6QQCv4/edit — verifica permisos</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>18</v>
-      </c>
-      <c r="B51" t="n">
-        <v>5</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Productos de Aseo</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2026-03-22T10:21:04.189600</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/Productos_de_Aseo_backup_20260322_101832.xlsx</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>ERROR exportando Sheet 1SKW_Tmk2H2V4OGKaELmVsvRmEe2x8UJJAKPdpTRimNg/edit — verifica permisos</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>17</v>
-      </c>
-      <c r="B52" t="n">
-        <v>4</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Panel Hosting</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2026-03-22T10:21:01.269981</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/Panel_Hosting_backup_20260322_101832.xlsx</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>ERROR exportando Sheet 1PXLNO-QL4bIqD_R4awEK71OunP7AUCysSZ5nWk4PqB0/edit — verifica permisos</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>16</v>
-      </c>
-      <c r="B53" t="n">
-        <v>3</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Admon Conjuntos</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2026-03-22T10:20:59.136831</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/Admon_Conjuntos_backup_20260322_101832.xlsx</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>ERROR exportando Sheet 1UqCfVwwQfAkzRHG4_YCX8BD3Xl95KB7qvwjZNXWkzKw/edit — verifica permisos</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>15</v>
-      </c>
-      <c r="B54" t="n">
-        <v>2</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Agenda Empresa serv.</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2026-03-22T10:20:55.590849</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/Agenda_Empresa_serv._backup_20260322_101832.xlsx</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>ERROR exportando Sheet 13UqQN6VXO9vTDIhyAEON9Qf5SD-1tgGgDA-Zo38udso/edit — verifica permisos</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>14</v>
-      </c>
-      <c r="B55" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>JAGT Landing Page</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2026-03-22T10:20:52.430736</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/JAGT_Landing_Page_backup_20260322_101832.xlsx</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>ERROR exportando Sheet 16F7ncXQJVmUJMMsl1So8FdfRZX9Vlo_nHkL9pWULjSE/edit — verifica permisos</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>13</v>
-      </c>
-      <c r="B56" t="n">
-        <v>9</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>AplicaionparaAbogadosp</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2026-03-22T10:20:48.650981</t>
-        </is>
-      </c>
-      <c r="E56" s="8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Estructura hosting exportada — AplicaionparaAbogadosp</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>12</v>
-      </c>
-      <c r="B57" t="n">
-        <v>8</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Plataforma Venta Permuta Vehiculos</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2026-03-22T10:20:44.187288</t>
-        </is>
-      </c>
-      <c r="E57" s="8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Estructura hosting exportada — Plataforma Venta Permuta Vehiculos</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>11</v>
-      </c>
-      <c r="B58" t="n">
-        <v>7</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Plataforma Autos Particulares</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2026-03-22T10:20:41.744104</t>
-        </is>
-      </c>
-      <c r="E58" s="8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Estructura hosting exportada — Plataforma Autos Particulares</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>10</v>
-      </c>
-      <c r="B59" t="n">
-        <v>6</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Clinica de Psicologia</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2026-03-22T10:20:39.360604</t>
-        </is>
-      </c>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Estructura hosting exportada — Clinica de Psicologia</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>9</v>
-      </c>
-      <c r="B60" t="n">
-        <v>5</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Productos de Aseo</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2026-03-22T10:20:38.428439</t>
-        </is>
-      </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Estructura hosting exportada — Productos de Aseo</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>8</v>
-      </c>
-      <c r="B61" t="n">
-        <v>4</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Panel Hosting</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2026-03-22T10:20:37.219042</t>
-        </is>
-      </c>
-      <c r="E61" s="8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Estructura hosting exportada — Panel Hosting</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>7</v>
-      </c>
-      <c r="B62" t="n">
-        <v>3</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Admon Conjuntos</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2026-03-22T10:20:36.528699</t>
-        </is>
-      </c>
-      <c r="E62" s="8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Estructura hosting exportada — Admon Conjuntos</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>6</v>
-      </c>
-      <c r="B63" t="n">
-        <v>2</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Agenda Empresa serv.</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2026-03-22T10:20:34.796287</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Estructura hosting exportada — Agenda Empresa serv.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>5</v>
-      </c>
-      <c r="B64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>JAGT Landing Page</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2026-03-22T10:20:34.113591</t>
-        </is>
-      </c>
-      <c r="E64" s="8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Google Drive/JAGT-Hosting/hosting-jagt.xlsx</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Estructura hosting exportada — JAGT Landing Page</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>4</v>
-      </c>
-      <c r="B65" t="n">
-        <v>8</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Plataforma Venta Permuta Vehiculos</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2026-03-21T14:29:06.529587</t>
-        </is>
-      </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>128.5</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Google Drive / hosting-jagt</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Backup manual desde panel</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>3</v>
-      </c>
-      <c r="B66" t="n">
-        <v>3</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Admon Conjuntos</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2026-03-21T11:11:20.734493</t>
-        </is>
-      </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>256</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Google Drive / hosting-jagt</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Backup manual desde panel</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>2</v>
-      </c>
-      <c r="B67" t="n">
-        <v>2</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Agenda Empresa serv.</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2026-03-21T11:01:03.298746</t>
-        </is>
-      </c>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>128.5</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Google Drive / hosting-jagt</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Backup manual desde panel</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>1</v>
-      </c>
-      <c r="B68" t="n">
-        <v>1</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>JAGT Landing Page</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2026-03-21T10:55:27.046758</t>
-        </is>
-      </c>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>256</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Local DB</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
         <is>
           <t>Backup manual desde panel</t>
         </is>
@@ -3733,7 +2221,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
     </row>
